--- a/data/materi_evaluasi.xlsx
+++ b/data/materi_evaluasi.xlsx
@@ -6864,6 +6864,9 @@
       <c r="D8" t="str">
         <v>XI - 1</v>
       </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>75</v>
       </c>
